--- a/eval/nomal_query_eval.xlsx
+++ b/eval/nomal_query_eval.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>TIMEOUT</t>
   </si>
@@ -47,13 +47,16 @@
     <t>Normal</t>
   </si>
   <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
     <t xml:space="preserve">avg dif</t>
   </si>
   <si>
     <t>median</t>
-  </si>
-  <si>
-    <t>std</t>
   </si>
   <si>
     <t>difference</t>
@@ -770,6 +773,13 @@
         <f t="shared" ref="B17:B21" si="0">B5</f>
         <v>Queries</v>
       </c>
+      <c r="O17" t="s">
+        <v>9</v>
+      </c>
+      <c r="P17">
+        <f>AVERAGE(C20:L22,C6:L6,C8:L10)</f>
+        <v>2.0671428571428572</v>
+      </c>
     </row>
     <row r="18" ht="14.25">
       <c r="B18" t="str">
@@ -816,6 +826,13 @@
         <f>A1</f>
         <v>TIMEOUT</v>
       </c>
+      <c r="O18" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18">
+        <f>STDEV(C6:L6,C8:L10,C20:L22)</f>
+        <v>2.2377344539829642</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
       <c r="B19" t="str">
@@ -862,13 +879,6 @@
         <f>A1</f>
         <v>TIMEOUT</v>
       </c>
-      <c r="O19" t="s">
-        <v>9</v>
-      </c>
-      <c r="P19">
-        <f>AVERAGE(C31:L33)</f>
-        <v>0.28333333333333327</v>
-      </c>
     </row>
     <row r="20" ht="14.25">
       <c r="B20" t="str">
@@ -906,11 +916,11 @@
         <v>1</v>
       </c>
       <c r="O20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P20">
-        <f>MEDIAN(C31:L33)</f>
-        <v>0.19999999999999996</v>
+        <f>AVERAGE(C31:L33)</f>
+        <v>0.28333333333333327</v>
       </c>
     </row>
     <row r="21" ht="14.25">
@@ -949,11 +959,11 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="O21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P21">
-        <f>STDEV(C31:L33)</f>
-        <v>0.30747394992918908</v>
+        <f>MEDIAN(C31:L33)</f>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="22" ht="14.25">
@@ -991,199 +1001,206 @@
       <c r="L22">
         <v>2.2000000000000002</v>
       </c>
+      <c r="O22" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22">
+        <f>STDEV(C31:L33)</f>
+        <v>0.30747394992918908</v>
+      </c>
     </row>
     <row r="27" ht="14.25">
       <c r="B27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" ht="14.25">
       <c r="B28" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B28:B32" si="1">B5</f>
         <v>Queries</v>
       </c>
     </row>
     <row r="29" ht="14.25">
       <c r="B29" t="str">
-        <f>B6</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">request the messages of liked users</v>
       </c>
       <c r="C29" t="e">
-        <f>C6-C18</f>
+        <f t="shared" ref="C29:C32" si="2">C6-C18</f>
         <v>#VALUE!</v>
       </c>
       <c r="D29" t="e">
-        <f>D6-D18</f>
+        <f t="shared" ref="D29:D32" si="3">D6-D18</f>
         <v>#VALUE!</v>
       </c>
       <c r="E29" t="e">
-        <f>E6-E18</f>
+        <f t="shared" ref="E29:E32" si="4">E6-E18</f>
         <v>#VALUE!</v>
       </c>
       <c r="F29" t="e">
-        <f>F6-F18</f>
+        <f t="shared" ref="F29:F32" si="5">F6-F18</f>
         <v>#VALUE!</v>
       </c>
       <c r="G29" t="e">
-        <f>G6-G18</f>
+        <f t="shared" ref="G29:G32" si="6">G6-G18</f>
         <v>#VALUE!</v>
       </c>
       <c r="H29" t="e">
-        <f>H6-H18</f>
+        <f t="shared" ref="H29:H32" si="7">H6-H18</f>
         <v>#VALUE!</v>
       </c>
       <c r="I29" t="e">
-        <f>I6-I18</f>
+        <f t="shared" ref="I29:I32" si="8">I6-I18</f>
         <v>#VALUE!</v>
       </c>
       <c r="J29" t="e">
-        <f>J6-J18</f>
+        <f t="shared" ref="J29:J32" si="9">J6-J18</f>
         <v>#VALUE!</v>
       </c>
       <c r="K29" t="e">
-        <f>K6-K18</f>
+        <f t="shared" ref="K29:K32" si="10">K6-K18</f>
         <v>#VALUE!</v>
       </c>
       <c r="L29" t="e">
-        <f>L6-L18</f>
+        <f t="shared" ref="L29:L32" si="11">L6-L18</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="B30" t="str">
-        <f>B7</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">request the forums a user posted</v>
       </c>
       <c r="C30" t="e">
-        <f>C7-C19</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="D30" t="e">
-        <f>D7-D19</f>
+        <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
       <c r="E30" t="e">
-        <f>E7-E19</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="F30" t="e">
-        <f>F7-F19</f>
+        <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="G30" t="e">
-        <f>G7-G19</f>
+        <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
       <c r="H30" t="e">
-        <f>H7-H19</f>
+        <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
       <c r="I30" t="e">
-        <f>I7-I19</f>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="J30" t="e">
-        <f>J7-J19</f>
+        <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
       <c r="K30" t="e">
-        <f>K7-K19</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="L30" t="e">
-        <f>L7-L19</f>
+        <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" ht="14.25">
       <c r="B31" t="str">
-        <f>B8</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">request the information of a user</v>
       </c>
       <c r="C31">
-        <f>C8-C20</f>
+        <f t="shared" si="2"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="D31">
-        <f>D8-D20</f>
+        <f t="shared" si="3"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="E31">
-        <f>E8-E20</f>
+        <f t="shared" si="4"/>
         <v>-0.10000000000000009</v>
       </c>
       <c r="F31">
-        <f>F8-F20</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G31">
-        <f>G8-G20</f>
+        <f t="shared" si="6"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="H31">
-        <f>H8-H20</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I31">
-        <f>I8-I20</f>
+        <f t="shared" si="8"/>
         <v>-0.10000000000000009</v>
       </c>
       <c r="J31">
-        <f>J8-J20</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K31">
-        <f>K8-K20</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L31">
-        <f>L8-L20</f>
+        <f t="shared" si="11"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
     <row r="32" ht="14.25">
       <c r="B32" t="str">
-        <f>B9</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">requests the post of a user</v>
       </c>
       <c r="C32">
-        <f>C9-C21</f>
+        <f t="shared" si="2"/>
         <v>0.20000000000000001</v>
       </c>
       <c r="D32">
-        <f>D9-D21</f>
+        <f t="shared" si="3"/>
         <v>0.099999999999999978</v>
       </c>
       <c r="E32">
-        <f>E9-E21</f>
+        <f t="shared" si="4"/>
         <v>0.099999999999999978</v>
       </c>
       <c r="F32">
-        <f>F9-F21</f>
+        <f t="shared" si="5"/>
         <v>0.20000000000000001</v>
       </c>
       <c r="G32">
-        <f>G9-G21</f>
+        <f t="shared" si="6"/>
         <v>0.20000000000000001</v>
       </c>
       <c r="H32">
-        <f>H9-H21</f>
+        <f t="shared" si="7"/>
         <v>0.20000000000000001</v>
       </c>
       <c r="I32">
-        <f>I9-I21</f>
+        <f t="shared" si="8"/>
         <v>0.20000000000000001</v>
       </c>
       <c r="J32">
-        <f>J9-J21</f>
+        <f t="shared" si="9"/>
         <v>0.099999999999999978</v>
       </c>
       <c r="K32">
-        <f>K9-K21</f>
+        <f t="shared" si="10"/>
         <v>0.099999999999999978</v>
       </c>
       <c r="L32">
-        <f>L9-L21</f>
+        <f t="shared" si="11"/>
         <v>0.099999999999999978</v>
       </c>
     </row>
